--- a/PREF350.xlsx
+++ b/PREF350.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C0FB91-F184-BE47-98DB-76D723A72806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{19DA4823-CB52-BA4A-932F-EF2D4EDF023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="emp_no" localSheetId="2">emp_no!$A$2:$I$393</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,8 +41,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{763F14B1-D4C4-CF4E-B405-49F8C87781C7}" name="emp_no" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="65001" sourceFile="/Users/nagu/Desktop/NVZ_SKD/emp_no.csv" comma="1">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="emp_no" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/nagu/Desktop/NVZ_SKD/emp_no.csv" comma="1">
       <textFields count="9">
         <textField/>
         <textField/>
@@ -2816,7 +2816,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3025,6 +3025,9 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3034,9 +3037,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3071,7 +3071,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="emp_no" connectionId="1" xr16:uid="{26AE79F9-3D17-0D43-B67C-ECA6649B0260}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="emp_no" connectionId="1" xr16:uid="{00000000-0016-0000-0200-000000000000}" autoFormatId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3360,16 +3360,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.5" customWidth="1"/>
-    <col min="5" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="41.04296875" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="36.54296875" customWidth="1"/>
+    <col min="5" max="6" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F11" s="11"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="F17" s="13"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="F19" s="14"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="F22" s="17"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A25" s="3" t="s">
         <v>18</v>
       </c>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F25" s="14"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
@@ -3777,19 +3777,19 @@
       </c>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:6" ht="16">
-      <c r="A28" s="22" t="s">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="20" t="s">
         <v>882</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22" t="s">
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19" t="s">
         <v>883</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="21" t="s">
         <v>884</v>
       </c>
     </row>
@@ -3807,9 +3807,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE8D720-6B51-E542-932C-E4AAB619F301}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>76</v>
       </c>
@@ -3826,18 +3826,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{991C2738-FE3E-A04F-890B-D204239BC212}">
   <dimension ref="A1:J393"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="7.49609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.04296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.99609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A2" t="s">
         <v>874</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A6" t="s">
         <v>103</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A9" t="s">
         <v>115</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A10" t="s">
         <v>119</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A11" t="s">
         <v>123</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A14" t="s">
         <v>133</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A15" t="s">
         <v>137</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A16" t="s">
         <v>140</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A17" t="s">
         <v>143</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A21" t="s">
         <v>140</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A28" t="s">
         <v>130</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A29" t="s">
         <v>140</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A35" t="s">
         <v>111</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A40" t="s">
         <v>119</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A41" t="s">
         <v>119</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A44" t="s">
         <v>137</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A46" t="s">
         <v>177</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A47" t="s">
         <v>177</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A48" t="s">
         <v>177</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A49" t="s">
         <v>177</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A50" t="s">
         <v>177</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A51" t="s">
         <v>177</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A52" t="s">
         <v>177</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A53" t="s">
         <v>177</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A54" t="s">
         <v>198</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A55" t="s">
         <v>198</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A56" t="s">
         <v>198</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A57" t="s">
         <v>198</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A58" t="s">
         <v>198</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A59" t="s">
         <v>198</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A60" t="s">
         <v>198</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A61" t="s">
         <v>198</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A62" t="s">
         <v>198</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A63" t="s">
         <v>198</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A64" t="s">
         <v>198</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A65" t="s">
         <v>198</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A66" t="s">
         <v>198</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A67" t="s">
         <v>198</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A68" t="s">
         <v>198</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A69" t="s">
         <v>198</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A70" t="s">
         <v>198</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A71" t="s">
         <v>198</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A72" t="s">
         <v>198</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A73" t="s">
         <v>198</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A74" t="s">
         <v>198</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A75" t="s">
         <v>198</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A76" t="s">
         <v>198</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A77" t="s">
         <v>198</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A78" t="s">
         <v>198</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A79" t="s">
         <v>198</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A80" t="s">
         <v>198</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A81" t="s">
         <v>198</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A82" t="s">
         <v>198</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A83" t="s">
         <v>198</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A84" t="s">
         <v>198</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A85" t="s">
         <v>198</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A87" t="s">
         <v>198</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A88" t="s">
         <v>198</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A89" t="s">
         <v>198</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A92" t="s">
         <v>198</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A93" t="s">
         <v>198</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A95" t="s">
         <v>198</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A96" t="s">
         <v>198</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A97" t="s">
         <v>198</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A98" t="s">
         <v>198</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A99" t="s">
         <v>198</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A101" t="s">
         <v>198</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A102" t="s">
         <v>198</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A103" t="s">
         <v>198</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A104" t="s">
         <v>198</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A105" t="s">
         <v>198</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A106" t="s">
         <v>198</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A107" t="s">
         <v>198</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A108" t="s">
         <v>198</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A109" t="s">
         <v>198</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A110" t="s">
         <v>323</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A111" t="s">
         <v>323</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A112" t="s">
         <v>323</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A113" t="s">
         <v>323</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A114" t="s">
         <v>323</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A115" t="s">
         <v>323</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A116" t="s">
         <v>323</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A117" t="s">
         <v>323</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A118" t="s">
         <v>323</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A119" t="s">
         <v>323</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A120" t="s">
         <v>323</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A121" t="s">
         <v>323</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A122" t="s">
         <v>349</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A123" t="s">
         <v>352</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A124" t="s">
         <v>352</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A125" t="s">
         <v>352</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A126" t="s">
         <v>352</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A127" t="s">
         <v>362</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A128" t="s">
         <v>86</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A129" t="s">
         <v>86</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A130" t="s">
         <v>86</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A131" t="s">
         <v>86</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A132" t="s">
         <v>86</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A133" t="s">
         <v>86</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A134" t="s">
         <v>86</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A135" t="s">
         <v>86</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A136" t="s">
         <v>86</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A137" t="s">
         <v>86</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A138" t="s">
         <v>86</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A139" t="s">
         <v>86</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A140" t="s">
         <v>86</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A141" t="s">
         <v>86</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A142" t="s">
         <v>86</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A143" t="s">
         <v>99</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A144" t="s">
         <v>99</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A145" t="s">
         <v>99</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A146" t="s">
         <v>99</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A147" t="s">
         <v>99</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A148" t="s">
         <v>99</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A149" t="s">
         <v>99</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A150" t="s">
         <v>99</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A151" t="s">
         <v>99</v>
       </c>
@@ -8126,7 +8126,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A152" t="s">
         <v>99</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A153" t="s">
         <v>99</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A154" t="s">
         <v>99</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A155" t="s">
         <v>99</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A156" t="s">
         <v>99</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A157" t="s">
         <v>99</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A158" t="s">
         <v>103</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A159" t="s">
         <v>103</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A160" t="s">
         <v>103</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A161" t="s">
         <v>103</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A162" t="s">
         <v>103</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A163" t="s">
         <v>103</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A164" t="s">
         <v>103</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A165" t="s">
         <v>103</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A166" t="s">
         <v>103</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A167" t="s">
         <v>103</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A168" t="s">
         <v>103</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A169" t="s">
         <v>103</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A170" t="s">
         <v>103</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A171" t="s">
         <v>103</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A172" t="s">
         <v>103</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A173" t="s">
         <v>103</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A174" t="s">
         <v>103</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A175" t="s">
         <v>107</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A176" t="s">
         <v>107</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A177" t="s">
         <v>107</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A178" t="s">
         <v>107</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A179" t="s">
         <v>107</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A180" t="s">
         <v>107</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A181" t="s">
         <v>107</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A182" t="s">
         <v>107</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A183" t="s">
         <v>107</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A184" t="s">
         <v>107</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A185" t="s">
         <v>107</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A186" t="s">
         <v>107</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A187" t="s">
         <v>107</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A188" t="s">
         <v>107</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A189" t="s">
         <v>107</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A190" t="s">
         <v>107</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A191" t="s">
         <v>111</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A192" t="s">
         <v>111</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A193" t="s">
         <v>111</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A194" t="s">
         <v>111</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A195" t="s">
         <v>111</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A196" t="s">
         <v>111</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A197" t="s">
         <v>111</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A198" t="s">
         <v>111</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A199" t="s">
         <v>111</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A200" t="s">
         <v>111</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A201" t="s">
         <v>111</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A202" t="s">
         <v>111</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A203" t="s">
         <v>111</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A204" t="s">
         <v>111</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A205" t="s">
         <v>111</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A206" t="s">
         <v>111</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A207" t="s">
         <v>91</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A208" t="s">
         <v>91</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A209" t="s">
         <v>91</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A210" t="s">
         <v>91</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A211" t="s">
         <v>91</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A212" t="s">
         <v>91</v>
       </c>
@@ -9679,7 +9679,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A213" t="s">
         <v>91</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A214" t="s">
         <v>91</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A216" t="s">
         <v>91</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A217" t="s">
         <v>91</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A218" t="s">
         <v>91</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A219" t="s">
         <v>91</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A220" t="s">
         <v>91</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A221" t="s">
         <v>91</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A222" t="s">
         <v>115</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A223" t="s">
         <v>115</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A224" t="s">
         <v>115</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A225" t="s">
         <v>115</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A226" t="s">
         <v>115</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A227" t="s">
         <v>115</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A228" t="s">
         <v>115</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A229" t="s">
         <v>115</v>
       </c>
@@ -10112,7 +10112,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A230" t="s">
         <v>115</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A231" t="s">
         <v>115</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A232" t="s">
         <v>115</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A233" t="s">
         <v>115</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A234" t="s">
         <v>115</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A235" t="s">
         <v>115</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A236" t="s">
         <v>115</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A237" t="s">
         <v>115</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A238" t="s">
         <v>119</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A239" t="s">
         <v>119</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A240" t="s">
         <v>119</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A241" t="s">
         <v>119</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A242" t="s">
         <v>119</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A243" t="s">
         <v>119</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A244" t="s">
         <v>119</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A245" t="s">
         <v>119</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A246" t="s">
         <v>119</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A247" t="s">
         <v>119</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A248" t="s">
         <v>119</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A249" t="s">
         <v>119</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A250" t="s">
         <v>119</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A251" t="s">
         <v>119</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A252" t="s">
         <v>123</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A253" t="s">
         <v>123</v>
       </c>
@@ -10706,7 +10706,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A254" t="s">
         <v>123</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A255" t="s">
         <v>123</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A256" t="s">
         <v>123</v>
       </c>
@@ -10793,7 +10793,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A257" t="s">
         <v>123</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A258" t="s">
         <v>123</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A259" t="s">
         <v>123</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A260" t="s">
         <v>123</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A261" t="s">
         <v>123</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A262" t="s">
         <v>123</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A263" t="s">
         <v>123</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A264" t="s">
         <v>123</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A265" t="s">
         <v>123</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A266" t="s">
         <v>123</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A267" t="s">
         <v>123</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A268" t="s">
         <v>123</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A269" t="s">
         <v>127</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A270" t="s">
         <v>127</v>
       </c>
@@ -11139,7 +11139,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A271" t="s">
         <v>127</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A272" t="s">
         <v>127</v>
       </c>
@@ -11197,7 +11197,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A273" t="s">
         <v>127</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A274" t="s">
         <v>127</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A275" t="s">
         <v>127</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A276" t="s">
         <v>127</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A277" t="s">
         <v>127</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A278" t="s">
         <v>127</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A279" t="s">
         <v>127</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A280" t="s">
         <v>127</v>
       </c>
@@ -11399,7 +11399,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A281" t="s">
         <v>127</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A282" t="s">
         <v>127</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A283" t="s">
         <v>127</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A284" t="s">
         <v>127</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A285" t="s">
         <v>127</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A286" t="s">
         <v>95</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A287" t="s">
         <v>95</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A288" t="s">
         <v>95</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A289" t="s">
         <v>95</v>
       </c>
@@ -11630,7 +11630,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A290" t="s">
         <v>95</v>
       </c>
@@ -11659,7 +11659,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A291" t="s">
         <v>95</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A292" t="s">
         <v>95</v>
       </c>
@@ -11711,7 +11711,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A293" t="s">
         <v>95</v>
       </c>
@@ -11734,7 +11734,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A294" t="s">
         <v>95</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A295" t="s">
         <v>95</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A296" t="s">
         <v>95</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A297" t="s">
         <v>95</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A298" t="s">
         <v>95</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A299" t="s">
         <v>95</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A300" t="s">
         <v>95</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A301" t="s">
         <v>95</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A302" t="s">
         <v>130</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A303" t="s">
         <v>130</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A304" t="s">
         <v>130</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A305" t="s">
         <v>130</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A306" t="s">
         <v>130</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A307" t="s">
         <v>130</v>
       </c>
@@ -12086,7 +12086,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A308" t="s">
         <v>130</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A309" t="s">
         <v>130</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A310" t="s">
         <v>130</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A311" t="s">
         <v>130</v>
       </c>
@@ -12178,7 +12178,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A312" t="s">
         <v>130</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A313" t="s">
         <v>130</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A314" t="s">
         <v>130</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A315" t="s">
         <v>130</v>
       </c>
@@ -12270,7 +12270,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A316" t="s">
         <v>130</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A317" t="s">
         <v>133</v>
       </c>
@@ -12322,7 +12322,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A318" t="s">
         <v>133</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A319" t="s">
         <v>133</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A320" t="s">
         <v>133</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A321" t="s">
         <v>133</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A322" t="s">
         <v>133</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A323" t="s">
         <v>133</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A324" t="s">
         <v>133</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A325" t="s">
         <v>133</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A326" t="s">
         <v>133</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A327" t="s">
         <v>133</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A328" t="s">
         <v>133</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A329" t="s">
         <v>133</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A330" t="s">
         <v>133</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A331" t="s">
         <v>133</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A332" t="s">
         <v>133</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A333" t="s">
         <v>133</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A334" t="s">
         <v>133</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A335" t="s">
         <v>137</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A336" t="s">
         <v>137</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A337" t="s">
         <v>137</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A338" t="s">
         <v>137</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A339" t="s">
         <v>137</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A340" t="s">
         <v>137</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A341" t="s">
         <v>137</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A342" t="s">
         <v>137</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A343" t="s">
         <v>137</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A344" t="s">
         <v>137</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A345" t="s">
         <v>137</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A346" t="s">
         <v>137</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A347" t="s">
         <v>137</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A348" t="s">
         <v>137</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A349" t="s">
         <v>137</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A350" t="s">
         <v>137</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A351" t="s">
         <v>137</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A352" t="s">
         <v>140</v>
       </c>
@@ -13217,7 +13217,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A353" t="s">
         <v>140</v>
       </c>
@@ -13246,7 +13246,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A354" t="s">
         <v>140</v>
       </c>
@@ -13275,7 +13275,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A355" t="s">
         <v>140</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A356" t="s">
         <v>140</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A357" t="s">
         <v>140</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A358" t="s">
         <v>140</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A359" t="s">
         <v>140</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A360" t="s">
         <v>140</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A361" t="s">
         <v>140</v>
       </c>
@@ -13448,7 +13448,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A362" t="s">
         <v>140</v>
       </c>
@@ -13471,7 +13471,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A363" t="s">
         <v>140</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A364" t="s">
         <v>140</v>
       </c>
@@ -13517,7 +13517,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A365" t="s">
         <v>140</v>
       </c>
@@ -13540,7 +13540,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A366" t="s">
         <v>820</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A367" t="s">
         <v>823</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A368" t="s">
         <v>826</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A369" t="s">
         <v>826</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A370" t="s">
         <v>826</v>
       </c>
@@ -13655,7 +13655,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A371" t="s">
         <v>833</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A372" t="s">
         <v>833</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A373" t="s">
         <v>837</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A374" t="s">
         <v>840</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A375" t="s">
         <v>840</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A376" t="s">
         <v>840</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A377" t="s">
         <v>840</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A378" t="s">
         <v>847</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A379" t="s">
         <v>847</v>
       </c>
@@ -13862,7 +13862,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A380" t="s">
         <v>847</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A381" t="s">
         <v>847</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A382" t="s">
         <v>847</v>
       </c>
@@ -13931,7 +13931,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A383" t="s">
         <v>847</v>
       </c>
@@ -13954,7 +13954,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A384" t="s">
         <v>847</v>
       </c>
@@ -13977,7 +13977,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A385" t="s">
         <v>847</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A386" t="s">
         <v>847</v>
       </c>
@@ -14023,7 +14023,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A387" t="s">
         <v>847</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A388" t="s">
         <v>847</v>
       </c>
@@ -14069,7 +14069,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A389" t="s">
         <v>847</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A390" t="s">
         <v>847</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A391" t="s">
         <v>847</v>
       </c>
@@ -14138,7 +14138,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A392" t="s">
         <v>847</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.1">
       <c r="A393" t="s">
         <v>78</v>
       </c>
@@ -14199,44 +14199,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA02B1F-9C6A-F043-8E69-5FE5B9EB8AD5}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="60" customHeight="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="A1" s="22" t="s">
         <v>875</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-    </row>
-    <row r="2" spans="1:14" ht="409" customHeight="1">
-      <c r="A2" s="21" t="str" cm="1">
-        <f t="array" ref="A2">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C3:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C)))&lt;&gt;"", "000"&amp;emp_no!C3:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C))), ""))</f>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+    </row>
+    <row r="2" spans="1:14" ht="408.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="24" t="str" cm="1">
+        <f t="array" aca="1" ref="A2" ca="1">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C3:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C)))&lt;&gt;"", "000"&amp;emp_no!C3:INDEX(emp_no!C:C, LOOKUP(2,1/(emp_no!C:C&lt;&gt;""), ROW(emp_no!C:C))), ""))</f>
         <v>00049147,00041511,00046107,00041672,00045104,00038579,00041492,00041478,00041331,00041271,00041675,00042420,00045105,00048688,00038564,00041571,00041333,00050842,00045585,00041554,00041339,00041371,00041850,00042072,00049580,00040592,00041334,00052029,00053803,00045618,00044492,00052011,00041666,00044490,00045588,00052031,00051354,00045150,00050879,00051290,00049582,00052030,00052032,00036758,00041205,00041512,00041493,00043014,00044484,00046104,00053806,00042725,00044009,00044007,00045117,00048783,00039615,00049043,00039645,00041268,00041668,00044005,00048143,00036756,00036777,00037756,00037761,00048687,00040593,00049290,00041396,00041556,00041337,00049148,00041498,00042073,00041507,00042075,00044397,00042422,00043854,00043861,00040618,00040568,00038587,00041685,00067838,00047991,00036147,00037243,00038260,00039243,00037741,00037726,00037750,00039617,00038569,00038593,00042244,00048673,00048684,00041317,00041323,00041661,00049111,00043652,00044966,00037706,00067673,00067393,00067851,00067904,00036184,00037238,00039665,00039684,00041283,00049121,00041484,00053747,00035740,00035216,00037743,00037732,00041486,00052461,00056911,00055023,00056895,00052215,00053894,00036963,00039238,00039668,00042423,00053768,00053787,00046043,00050843,00051138,00052467,00055022,00057515,00056893,00053861,00052212,00036185,00053733,00039671,00048682,00049136,00053759,00053849,00045116,00045154,00054386,00058950,00056900,00057462,00053807,00052196,00052209,00036965,00040560,00041304,00049411,00042084,00041705,00044415,00053816,00045589,00045960,00056565,00054373,00055007,00056894,00057472,00052193,00067337,00037698,00040781,00053740,00040612,00042419,00045108,00045152,00050880,00051140,00057243,00055045,00056896,00057464,00053858,00052213,00053901,00037716,00039646,00038575,00040620,00043461,00042247,00045586,00045619,00045950,00054376,00058951,00056866,00052189,00052586,00036150,00036968,00049074,00039673,00040624,00041181,00053767,00044962,00045587,00041206,00056581,00055025,00056873,00057449,00053855,00052211,00053902,00039630,00037763,00039667,00053735,00041191,00041703,00044983,00045151,00045621,00054377,00055013,00057497,00053857,00052214,00053805,00067836,00039611,00040970,00039633,00040611,00041742,00046041,00045957,00054378,00056853,00056865,00057498,00052191,00052207,00052587,00035738,00038568,00039683,00041187,00053781,00041696,00044388,00044975,00044493,00052012,00056617,00054367,00056912,00056864,00056860,00053863,00053898,00051139,00048174,00040790,00048678,00040563,00053732,00050290,00044977,00050841,00051355,00054374,00056877,00058953,00053860,00052210,00053895,00036754,00038537,00038546,00048680,00053742,00041325,00044974,00046106,00046039,00051289,00052465,00055050,00056876,00057490,00052190,00053802,00036971,00037729,00038583,00041188,00049410,00042724,00044950,00045115,00045584,00056692,00057247,00055044,00056862,00056882,00057511,00052188,00053892,00053810,00067852,00035737,00040259,00038559,00041468,00044952,00045593,00045149,00045617,00052463,00056849,00054381,00057244,00056906,00057459,00052192,00067753,00038262,00039357,00049155,00049394,00049332,00044530,00045118,00050881,00045616,00054385,00055036,00058952,00053859,00052195,00048026,00049047,00040783,00048691,00053739,00043862,00044486,00046040,00051326,00040973,00040599,00044396,00045113,00051291,00041336,00045114,00038590,00036748,00039641,00039681,00039629,00041204,00048993,00040269,00044394,00057451,00056897,00057454,00057471,00057510,00057483,00057460,00058367,00053896,00057475,00057484,000社員番号</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14251,9 +14251,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -14281,7 +14281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A3" t="s">
         <v>9</v>
       </c>
